--- a/Nifty50_All_17_Quarters_RealTime_Execution_Master_Audited.xlsx
+++ b/Nifty50_All_17_Quarters_RealTime_Execution_Master_Audited.xlsx
@@ -539,7 +539,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N54"/>
+  <dimension ref="A1:N53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -930,67 +930,67 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>EICHERMOT</t>
+          <t>JIOFIN</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>Eicher Motors Ltd</t>
-        </is>
-      </c>
-      <c r="D9" s="9" t="inlineStr">
-        <is>
-          <t>LONG</t>
+          <t>Jio Financial Services Ltd</t>
+        </is>
+      </c>
+      <c r="D9" s="6" t="inlineStr">
+        <is>
+          <t>SHORT</t>
         </is>
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>T-4 to T+1</t>
+          <t>T-1 to T+7</t>
         </is>
       </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>T - 4</t>
+          <t>T - 1</t>
         </is>
       </c>
       <c r="G9" s="4" t="inlineStr">
         <is>
-          <t>T + 1</t>
+          <t>T + 7</t>
         </is>
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>86.6%</t>
+          <t>83.3%</t>
         </is>
       </c>
       <c r="I9" s="4" t="inlineStr">
         <is>
-          <t>84.0%</t>
+          <t>92.7%</t>
         </is>
       </c>
       <c r="J9" s="7" t="inlineStr">
         <is>
-          <t>₹12,052</t>
+          <t>₹16,054</t>
         </is>
       </c>
       <c r="K9" s="7" t="inlineStr">
         <is>
-          <t>₹27,840</t>
-        </is>
-      </c>
-      <c r="L9" s="10" t="inlineStr">
+          <t>₹104,429</t>
+        </is>
+      </c>
+      <c r="L9" s="8" t="inlineStr">
         <is>
           <t>NOT ANNOUNCED YET</t>
         </is>
       </c>
       <c r="M9" s="5" t="inlineStr">
         <is>
-          <t>BUY FUTURES 4 trading days before T, Exit 1 days after T</t>
+          <t>SELL FUTURES 1 trading days before T, Exit 7 days after T</t>
         </is>
       </c>
       <c r="N9" s="5" t="inlineStr">
         <is>
-          <t>BUY CALL OPTION 4 trading days before T</t>
+          <t>BUY PUT OPTION 1 trading days before T</t>
         </is>
       </c>
     </row>
@@ -1000,12 +1000,12 @@
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>CIPLA</t>
+          <t>TMPV</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>Cipla Ltd</t>
+          <t>Tata Motors Passenger Vehicles Ltd</t>
         </is>
       </c>
       <c r="D10" s="9" t="inlineStr">
@@ -1015,52 +1015,52 @@
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>T-6 to T+4</t>
+          <t>T-2 to T+3</t>
         </is>
       </c>
       <c r="F10" s="4" t="inlineStr">
         <is>
-          <t>T - 6</t>
+          <t>T - 2</t>
         </is>
       </c>
       <c r="G10" s="4" t="inlineStr">
         <is>
-          <t>T + 4</t>
+          <t>T + 3</t>
         </is>
       </c>
       <c r="H10" s="4" t="inlineStr">
         <is>
-          <t>87.0%</t>
+          <t>73.9%</t>
         </is>
       </c>
       <c r="I10" s="4" t="inlineStr">
         <is>
-          <t>83.8%</t>
+          <t>89.6%</t>
         </is>
       </c>
       <c r="J10" s="7" t="inlineStr">
         <is>
-          <t>₹108,768</t>
+          <t>₹3,462</t>
         </is>
       </c>
       <c r="K10" s="7" t="inlineStr">
         <is>
-          <t>₹250,099</t>
-        </is>
-      </c>
-      <c r="L10" s="10" t="inlineStr">
+          <t>₹44,952</t>
+        </is>
+      </c>
+      <c r="L10" s="8" t="inlineStr">
         <is>
           <t>NOT ANNOUNCED YET</t>
         </is>
       </c>
       <c r="M10" s="5" t="inlineStr">
         <is>
-          <t>BUY FUTURES 6 trading days before T, Exit 4 days after T</t>
+          <t>BUY FUTURES 2 trading days before T, Exit 3 days after T</t>
         </is>
       </c>
       <c r="N10" s="5" t="inlineStr">
         <is>
-          <t>BUY CALL OPTION 6 trading days before T</t>
+          <t>BUY CALL OPTION 2 trading days before T</t>
         </is>
       </c>
     </row>
@@ -1070,67 +1070,67 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>ITC</t>
+          <t>MAXHEALTH</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>ITC Ltd</t>
-        </is>
-      </c>
-      <c r="D11" s="6" t="inlineStr">
-        <is>
-          <t>SHORT</t>
+          <t>Max Healthcare Institute Ltd</t>
+        </is>
+      </c>
+      <c r="D11" s="9" t="inlineStr">
+        <is>
+          <t>LONG</t>
         </is>
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>T-2 to T+1</t>
+          <t>T-8 to T+5</t>
         </is>
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>T - 2</t>
+          <t>T - 8</t>
         </is>
       </c>
       <c r="G11" s="4" t="inlineStr">
         <is>
-          <t>T + 1</t>
+          <t>T + 5</t>
         </is>
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>84.6%</t>
+          <t>73.9%</t>
         </is>
       </c>
       <c r="I11" s="4" t="inlineStr">
         <is>
-          <t>83.4%</t>
+          <t>88.5%</t>
         </is>
       </c>
       <c r="J11" s="7" t="inlineStr">
         <is>
-          <t>₹334,660</t>
+          <t>₹26,079</t>
         </is>
       </c>
       <c r="K11" s="7" t="inlineStr">
         <is>
-          <t>₹791,533</t>
-        </is>
-      </c>
-      <c r="L11" s="10" t="inlineStr">
+          <t>₹103,120</t>
+        </is>
+      </c>
+      <c r="L11" s="8" t="inlineStr">
         <is>
           <t>NOT ANNOUNCED YET</t>
         </is>
       </c>
       <c r="M11" s="5" t="inlineStr">
         <is>
-          <t>SELL FUTURES 2 trading days before T, Exit 1 days after T</t>
+          <t>BUY FUTURES 8 trading days before T, Exit 5 days after T</t>
         </is>
       </c>
       <c r="N11" s="5" t="inlineStr">
         <is>
-          <t>BUY PUT OPTION 2 trading days before T</t>
+          <t>BUY CALL OPTION 8 trading days before T</t>
         </is>
       </c>
     </row>
@@ -1140,52 +1140,52 @@
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>WIPRO</t>
+          <t>EICHERMOT</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>Wipro Ltd</t>
-        </is>
-      </c>
-      <c r="D12" s="6" t="inlineStr">
-        <is>
-          <t>SHORT</t>
+          <t>Eicher Motors Ltd</t>
+        </is>
+      </c>
+      <c r="D12" s="9" t="inlineStr">
+        <is>
+          <t>LONG</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>T-3 to T+5</t>
+          <t>T-4 to T+1</t>
         </is>
       </c>
       <c r="F12" s="4" t="inlineStr">
         <is>
-          <t>T - 3</t>
+          <t>T - 4</t>
         </is>
       </c>
       <c r="G12" s="4" t="inlineStr">
         <is>
-          <t>T + 5</t>
+          <t>T + 1</t>
         </is>
       </c>
       <c r="H12" s="4" t="inlineStr">
         <is>
-          <t>85.6%</t>
+          <t>86.6%</t>
         </is>
       </c>
       <c r="I12" s="4" t="inlineStr">
         <is>
-          <t>83.3%</t>
+          <t>84.0%</t>
         </is>
       </c>
       <c r="J12" s="7" t="inlineStr">
         <is>
-          <t>₹405,519</t>
+          <t>₹12,052</t>
         </is>
       </c>
       <c r="K12" s="7" t="inlineStr">
         <is>
-          <t>₹947,586</t>
+          <t>₹27,840</t>
         </is>
       </c>
       <c r="L12" s="10" t="inlineStr">
@@ -1195,12 +1195,12 @@
       </c>
       <c r="M12" s="5" t="inlineStr">
         <is>
-          <t>SELL FUTURES 3 trading days before T, Exit 5 days after T</t>
+          <t>BUY FUTURES 4 trading days before T, Exit 1 days after T</t>
         </is>
       </c>
       <c r="N12" s="5" t="inlineStr">
         <is>
-          <t>BUY PUT OPTION 3 trading days before T</t>
+          <t>BUY CALL OPTION 4 trading days before T</t>
         </is>
       </c>
     </row>
@@ -1210,12 +1210,12 @@
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>ADANIPORTS</t>
+          <t>CIPLA</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>Adani Ports &amp; SEZ Ltd</t>
+          <t>Cipla Ltd</t>
         </is>
       </c>
       <c r="D13" s="9" t="inlineStr">
@@ -1225,37 +1225,37 @@
       </c>
       <c r="E13" s="4" t="inlineStr">
         <is>
-          <t>T-4 to T+5</t>
+          <t>T-6 to T+4</t>
         </is>
       </c>
       <c r="F13" s="4" t="inlineStr">
         <is>
-          <t>T - 4</t>
+          <t>T - 6</t>
         </is>
       </c>
       <c r="G13" s="4" t="inlineStr">
         <is>
-          <t>T + 5</t>
+          <t>T + 4</t>
         </is>
       </c>
       <c r="H13" s="4" t="inlineStr">
         <is>
-          <t>74.9%</t>
+          <t>87.0%</t>
         </is>
       </c>
       <c r="I13" s="4" t="inlineStr">
         <is>
-          <t>82.6%</t>
+          <t>83.8%</t>
         </is>
       </c>
       <c r="J13" s="7" t="inlineStr">
         <is>
-          <t>₹71,088</t>
+          <t>₹108,768</t>
         </is>
       </c>
       <c r="K13" s="7" t="inlineStr">
         <is>
-          <t>₹189,923</t>
+          <t>₹250,099</t>
         </is>
       </c>
       <c r="L13" s="10" t="inlineStr">
@@ -1265,12 +1265,12 @@
       </c>
       <c r="M13" s="5" t="inlineStr">
         <is>
-          <t>BUY FUTURES 4 trading days before T, Exit 5 days after T</t>
+          <t>BUY FUTURES 6 trading days before T, Exit 4 days after T</t>
         </is>
       </c>
       <c r="N13" s="5" t="inlineStr">
         <is>
-          <t>BUY CALL OPTION 4 trading days before T</t>
+          <t>BUY CALL OPTION 6 trading days before T</t>
         </is>
       </c>
     </row>
@@ -1280,12 +1280,12 @@
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>ICICIBANK</t>
+          <t>ITC</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>ICICI Bank Ltd</t>
+          <t>ITC Ltd</t>
         </is>
       </c>
       <c r="D14" s="6" t="inlineStr">
@@ -1295,37 +1295,37 @@
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>T-6 to T+4</t>
+          <t>T-2 to T+1</t>
         </is>
       </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
-          <t>T - 6</t>
+          <t>T - 2</t>
         </is>
       </c>
       <c r="G14" s="4" t="inlineStr">
         <is>
-          <t>T + 4</t>
+          <t>T + 1</t>
         </is>
       </c>
       <c r="H14" s="4" t="inlineStr">
         <is>
-          <t>73.6%</t>
+          <t>84.6%</t>
         </is>
       </c>
       <c r="I14" s="4" t="inlineStr">
         <is>
-          <t>82.6%</t>
+          <t>83.4%</t>
         </is>
       </c>
       <c r="J14" s="7" t="inlineStr">
         <is>
-          <t>₹91,950</t>
+          <t>₹334,660</t>
         </is>
       </c>
       <c r="K14" s="7" t="inlineStr">
         <is>
-          <t>₹249,899</t>
+          <t>₹791,533</t>
         </is>
       </c>
       <c r="L14" s="10" t="inlineStr">
@@ -1335,12 +1335,12 @@
       </c>
       <c r="M14" s="5" t="inlineStr">
         <is>
-          <t>SELL FUTURES 6 trading days before T, Exit 4 days after T</t>
+          <t>SELL FUTURES 2 trading days before T, Exit 1 days after T</t>
         </is>
       </c>
       <c r="N14" s="5" t="inlineStr">
         <is>
-          <t>BUY PUT OPTION 6 trading days before T</t>
+          <t>BUY PUT OPTION 2 trading days before T</t>
         </is>
       </c>
     </row>
@@ -1350,52 +1350,52 @@
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>DIVISLAB</t>
+          <t>WIPRO</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>Divis Laboratories Ltd</t>
-        </is>
-      </c>
-      <c r="D15" s="9" t="inlineStr">
-        <is>
-          <t>LONG</t>
+          <t>Wipro Ltd</t>
+        </is>
+      </c>
+      <c r="D15" s="6" t="inlineStr">
+        <is>
+          <t>SHORT</t>
         </is>
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
-          <t>T-4 to T+3</t>
+          <t>T-3 to T+5</t>
         </is>
       </c>
       <c r="F15" s="4" t="inlineStr">
         <is>
-          <t>T - 4</t>
+          <t>T - 3</t>
         </is>
       </c>
       <c r="G15" s="4" t="inlineStr">
         <is>
-          <t>T + 3</t>
+          <t>T + 5</t>
         </is>
       </c>
       <c r="H15" s="4" t="inlineStr">
         <is>
-          <t>83.6%</t>
+          <t>85.6%</t>
         </is>
       </c>
       <c r="I15" s="4" t="inlineStr">
         <is>
-          <t>82.5%</t>
+          <t>83.3%</t>
         </is>
       </c>
       <c r="J15" s="7" t="inlineStr">
         <is>
-          <t>₹21,486</t>
+          <t>₹405,519</t>
         </is>
       </c>
       <c r="K15" s="7" t="inlineStr">
         <is>
-          <t>₹51,395</t>
+          <t>₹947,586</t>
         </is>
       </c>
       <c r="L15" s="10" t="inlineStr">
@@ -1405,12 +1405,12 @@
       </c>
       <c r="M15" s="5" t="inlineStr">
         <is>
-          <t>BUY FUTURES 4 trading days before T, Exit 3 days after T</t>
+          <t>SELL FUTURES 3 trading days before T, Exit 5 days after T</t>
         </is>
       </c>
       <c r="N15" s="5" t="inlineStr">
         <is>
-          <t>BUY CALL OPTION 4 trading days before T</t>
+          <t>BUY PUT OPTION 3 trading days before T</t>
         </is>
       </c>
     </row>
@@ -1420,52 +1420,52 @@
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>HDFCBANK</t>
+          <t>ADANIPORTS</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>HDFC Bank Ltd</t>
-        </is>
-      </c>
-      <c r="D16" s="6" t="inlineStr">
-        <is>
-          <t>SHORT</t>
+          <t>Adani Ports &amp; SEZ Ltd</t>
+        </is>
+      </c>
+      <c r="D16" s="9" t="inlineStr">
+        <is>
+          <t>LONG</t>
         </is>
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>T-6 to T+3</t>
+          <t>T-4 to T+5</t>
         </is>
       </c>
       <c r="F16" s="4" t="inlineStr">
         <is>
-          <t>T - 6</t>
+          <t>T - 4</t>
         </is>
       </c>
       <c r="G16" s="4" t="inlineStr">
         <is>
-          <t>T + 3</t>
+          <t>T + 5</t>
         </is>
       </c>
       <c r="H16" s="4" t="inlineStr">
         <is>
-          <t>89.0%</t>
+          <t>74.9%</t>
         </is>
       </c>
       <c r="I16" s="4" t="inlineStr">
         <is>
-          <t>82.5%</t>
+          <t>82.6%</t>
         </is>
       </c>
       <c r="J16" s="7" t="inlineStr">
         <is>
-          <t>₹91,105</t>
+          <t>₹71,088</t>
         </is>
       </c>
       <c r="K16" s="7" t="inlineStr">
         <is>
-          <t>₹204,708</t>
+          <t>₹189,923</t>
         </is>
       </c>
       <c r="L16" s="10" t="inlineStr">
@@ -1475,12 +1475,12 @@
       </c>
       <c r="M16" s="5" t="inlineStr">
         <is>
-          <t>SELL FUTURES 6 trading days before T, Exit 3 days after T</t>
+          <t>BUY FUTURES 4 trading days before T, Exit 5 days after T</t>
         </is>
       </c>
       <c r="N16" s="5" t="inlineStr">
         <is>
-          <t>BUY PUT OPTION 6 trading days before T</t>
+          <t>BUY CALL OPTION 4 trading days before T</t>
         </is>
       </c>
     </row>
@@ -1490,52 +1490,52 @@
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>APOLLOHOSP</t>
+          <t>ICICIBANK</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>Apollo Hospitals Enterprise Ltd</t>
-        </is>
-      </c>
-      <c r="D17" s="9" t="inlineStr">
-        <is>
-          <t>LONG</t>
+          <t>ICICI Bank Ltd</t>
+        </is>
+      </c>
+      <c r="D17" s="6" t="inlineStr">
+        <is>
+          <t>SHORT</t>
         </is>
       </c>
       <c r="E17" s="4" t="inlineStr">
         <is>
-          <t>T-3 to T+3</t>
+          <t>T-6 to T+4</t>
         </is>
       </c>
       <c r="F17" s="4" t="inlineStr">
         <is>
-          <t>T - 3</t>
+          <t>T - 6</t>
         </is>
       </c>
       <c r="G17" s="4" t="inlineStr">
         <is>
-          <t>T + 3</t>
+          <t>T + 4</t>
         </is>
       </c>
       <c r="H17" s="4" t="inlineStr">
         <is>
-          <t>70.3%</t>
+          <t>73.6%</t>
         </is>
       </c>
       <c r="I17" s="4" t="inlineStr">
         <is>
-          <t>82.4%</t>
+          <t>82.6%</t>
         </is>
       </c>
       <c r="J17" s="7" t="inlineStr">
         <is>
-          <t>₹12,079</t>
+          <t>₹91,950</t>
         </is>
       </c>
       <c r="K17" s="7" t="inlineStr">
         <is>
-          <t>₹34,348</t>
+          <t>₹249,899</t>
         </is>
       </c>
       <c r="L17" s="10" t="inlineStr">
@@ -1545,12 +1545,12 @@
       </c>
       <c r="M17" s="5" t="inlineStr">
         <is>
-          <t>BUY FUTURES 3 trading days before T, Exit 3 days after T</t>
+          <t>SELL FUTURES 6 trading days before T, Exit 4 days after T</t>
         </is>
       </c>
       <c r="N17" s="5" t="inlineStr">
         <is>
-          <t>BUY CALL OPTION 3 trading days before T</t>
+          <t>BUY PUT OPTION 6 trading days before T</t>
         </is>
       </c>
     </row>
@@ -1560,22 +1560,22 @@
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>ADANIENT</t>
+          <t>HDFCBANK</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>Adani Enterprises Ltd</t>
-        </is>
-      </c>
-      <c r="D18" s="9" t="inlineStr">
-        <is>
-          <t>LONG</t>
+          <t>HDFC Bank Ltd</t>
+        </is>
+      </c>
+      <c r="D18" s="6" t="inlineStr">
+        <is>
+          <t>SHORT</t>
         </is>
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>T-6 to T+4</t>
+          <t>T-6 to T+3</t>
         </is>
       </c>
       <c r="F18" s="4" t="inlineStr">
@@ -1585,27 +1585,27 @@
       </c>
       <c r="G18" s="4" t="inlineStr">
         <is>
-          <t>T + 4</t>
+          <t>T + 3</t>
         </is>
       </c>
       <c r="H18" s="4" t="inlineStr">
         <is>
-          <t>79.5%</t>
+          <t>89.0%</t>
         </is>
       </c>
       <c r="I18" s="4" t="inlineStr">
         <is>
-          <t>82.0%</t>
+          <t>82.5%</t>
         </is>
       </c>
       <c r="J18" s="7" t="inlineStr">
         <is>
-          <t>₹58,502</t>
+          <t>₹91,105</t>
         </is>
       </c>
       <c r="K18" s="7" t="inlineStr">
         <is>
-          <t>₹147,248</t>
+          <t>₹204,708</t>
         </is>
       </c>
       <c r="L18" s="10" t="inlineStr">
@@ -1615,12 +1615,12 @@
       </c>
       <c r="M18" s="5" t="inlineStr">
         <is>
-          <t>BUY FUTURES 6 trading days before T, Exit 4 days after T</t>
+          <t>SELL FUTURES 6 trading days before T, Exit 3 days after T</t>
         </is>
       </c>
       <c r="N18" s="5" t="inlineStr">
         <is>
-          <t>BUY CALL OPTION 6 trading days before T</t>
+          <t>BUY PUT OPTION 6 trading days before T</t>
         </is>
       </c>
     </row>
@@ -1630,52 +1630,52 @@
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>HDFCLIFE</t>
+          <t>APOLLOHOSP</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>HDFC Life Insurance Co Ltd</t>
-        </is>
-      </c>
-      <c r="D19" s="6" t="inlineStr">
-        <is>
-          <t>SHORT</t>
+          <t>Apollo Hospitals Enterprise Ltd</t>
+        </is>
+      </c>
+      <c r="D19" s="9" t="inlineStr">
+        <is>
+          <t>LONG</t>
         </is>
       </c>
       <c r="E19" s="4" t="inlineStr">
         <is>
-          <t>T-7 to T+2</t>
+          <t>T-3 to T+3</t>
         </is>
       </c>
       <c r="F19" s="4" t="inlineStr">
         <is>
-          <t>T - 7</t>
+          <t>T - 3</t>
         </is>
       </c>
       <c r="G19" s="4" t="inlineStr">
         <is>
-          <t>T + 2</t>
+          <t>T + 3</t>
         </is>
       </c>
       <c r="H19" s="4" t="inlineStr">
         <is>
-          <t>90.8%</t>
+          <t>70.3%</t>
         </is>
       </c>
       <c r="I19" s="4" t="inlineStr">
         <is>
-          <t>82.0%</t>
+          <t>82.4%</t>
         </is>
       </c>
       <c r="J19" s="7" t="inlineStr">
         <is>
-          <t>₹100,336</t>
+          <t>₹12,079</t>
         </is>
       </c>
       <c r="K19" s="7" t="inlineStr">
         <is>
-          <t>₹220,931</t>
+          <t>₹34,348</t>
         </is>
       </c>
       <c r="L19" s="10" t="inlineStr">
@@ -1685,12 +1685,12 @@
       </c>
       <c r="M19" s="5" t="inlineStr">
         <is>
-          <t>SELL FUTURES 7 trading days before T, Exit 2 days after T</t>
+          <t>BUY FUTURES 3 trading days before T, Exit 3 days after T</t>
         </is>
       </c>
       <c r="N19" s="5" t="inlineStr">
         <is>
-          <t>BUY PUT OPTION 7 trading days before T</t>
+          <t>BUY CALL OPTION 3 trading days before T</t>
         </is>
       </c>
     </row>
@@ -1700,12 +1700,12 @@
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>TCS</t>
+          <t>ETERNAL</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services Ltd</t>
+          <t>Eternal Ltd</t>
         </is>
       </c>
       <c r="D20" s="9" t="inlineStr">
@@ -1715,52 +1715,52 @@
       </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
-          <t>T-2 to T+4</t>
+          <t>T-7 to T+7</t>
         </is>
       </c>
       <c r="F20" s="4" t="inlineStr">
         <is>
-          <t>T - 2</t>
+          <t>T - 7</t>
         </is>
       </c>
       <c r="G20" s="4" t="inlineStr">
         <is>
-          <t>T + 4</t>
+          <t>T + 7</t>
         </is>
       </c>
       <c r="H20" s="4" t="inlineStr">
         <is>
-          <t>85.3%</t>
+          <t>71.4%</t>
         </is>
       </c>
       <c r="I20" s="4" t="inlineStr">
         <is>
-          <t>81.7%</t>
+          <t>82.4%</t>
         </is>
       </c>
       <c r="J20" s="7" t="inlineStr">
         <is>
-          <t>₹36,972</t>
+          <t>₹47,978</t>
         </is>
       </c>
       <c r="K20" s="7" t="inlineStr">
         <is>
-          <t>₹86,687</t>
-        </is>
-      </c>
-      <c r="L20" s="10" t="inlineStr">
+          <t>₹159,007</t>
+        </is>
+      </c>
+      <c r="L20" s="8" t="inlineStr">
         <is>
           <t>NOT ANNOUNCED YET</t>
         </is>
       </c>
       <c r="M20" s="5" t="inlineStr">
         <is>
-          <t>BUY FUTURES 2 trading days before T, Exit 4 days after T</t>
+          <t>BUY FUTURES 7 trading days before T, Exit 7 days after T</t>
         </is>
       </c>
       <c r="N20" s="5" t="inlineStr">
         <is>
-          <t>BUY CALL OPTION 2 trading days before T</t>
+          <t>BUY CALL OPTION 7 trading days before T</t>
         </is>
       </c>
     </row>
@@ -1770,12 +1770,12 @@
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>INDIGO</t>
+          <t>ADANIENT</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>InterGlobe Aviation Ltd</t>
+          <t>Adani Enterprises Ltd</t>
         </is>
       </c>
       <c r="D21" s="9" t="inlineStr">
@@ -1785,37 +1785,37 @@
       </c>
       <c r="E21" s="4" t="inlineStr">
         <is>
-          <t>T-2 to T+5</t>
+          <t>T-6 to T+4</t>
         </is>
       </c>
       <c r="F21" s="4" t="inlineStr">
         <is>
-          <t>T - 2</t>
+          <t>T - 6</t>
         </is>
       </c>
       <c r="G21" s="4" t="inlineStr">
         <is>
-          <t>T + 5</t>
+          <t>T + 4</t>
         </is>
       </c>
       <c r="H21" s="4" t="inlineStr">
         <is>
-          <t>91.1%</t>
+          <t>79.5%</t>
         </is>
       </c>
       <c r="I21" s="4" t="inlineStr">
         <is>
-          <t>81.6%</t>
+          <t>82.0%</t>
         </is>
       </c>
       <c r="J21" s="7" t="inlineStr">
         <is>
-          <t>₹21,244</t>
+          <t>₹58,502</t>
         </is>
       </c>
       <c r="K21" s="7" t="inlineStr">
         <is>
-          <t>₹46,648</t>
+          <t>₹147,248</t>
         </is>
       </c>
       <c r="L21" s="10" t="inlineStr">
@@ -1825,12 +1825,12 @@
       </c>
       <c r="M21" s="5" t="inlineStr">
         <is>
-          <t>BUY FUTURES 2 trading days before T, Exit 5 days after T</t>
+          <t>BUY FUTURES 6 trading days before T, Exit 4 days after T</t>
         </is>
       </c>
       <c r="N21" s="5" t="inlineStr">
         <is>
-          <t>BUY CALL OPTION 2 trading days before T</t>
+          <t>BUY CALL OPTION 6 trading days before T</t>
         </is>
       </c>
     </row>
@@ -1840,52 +1840,52 @@
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>HINDALCO</t>
+          <t>HDFCLIFE</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>Hindalco Industries Ltd</t>
-        </is>
-      </c>
-      <c r="D22" s="9" t="inlineStr">
-        <is>
-          <t>LONG</t>
+          <t>HDFC Life Insurance Co Ltd</t>
+        </is>
+      </c>
+      <c r="D22" s="6" t="inlineStr">
+        <is>
+          <t>SHORT</t>
         </is>
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
-          <t>T-4 to T+1</t>
+          <t>T-7 to T+2</t>
         </is>
       </c>
       <c r="F22" s="4" t="inlineStr">
         <is>
-          <t>T - 4</t>
+          <t>T - 7</t>
         </is>
       </c>
       <c r="G22" s="4" t="inlineStr">
         <is>
-          <t>T + 1</t>
+          <t>T + 2</t>
         </is>
       </c>
       <c r="H22" s="4" t="inlineStr">
         <is>
-          <t>85.8%</t>
+          <t>90.8%</t>
         </is>
       </c>
       <c r="I22" s="4" t="inlineStr">
         <is>
-          <t>81.5%</t>
+          <t>82.0%</t>
         </is>
       </c>
       <c r="J22" s="7" t="inlineStr">
         <is>
-          <t>₹287,445</t>
+          <t>₹100,336</t>
         </is>
       </c>
       <c r="K22" s="7" t="inlineStr">
         <is>
-          <t>₹670,270</t>
+          <t>₹220,931</t>
         </is>
       </c>
       <c r="L22" s="10" t="inlineStr">
@@ -1895,12 +1895,12 @@
       </c>
       <c r="M22" s="5" t="inlineStr">
         <is>
-          <t>BUY FUTURES 4 trading days before T, Exit 1 days after T</t>
+          <t>SELL FUTURES 7 trading days before T, Exit 2 days after T</t>
         </is>
       </c>
       <c r="N22" s="5" t="inlineStr">
         <is>
-          <t>BUY CALL OPTION 4 trading days before T</t>
+          <t>BUY PUT OPTION 7 trading days before T</t>
         </is>
       </c>
     </row>
@@ -1910,12 +1910,12 @@
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>TATASTEEL</t>
+          <t>TCS</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>Tata Steel Ltd</t>
+          <t>Tata Consultancy Services Ltd</t>
         </is>
       </c>
       <c r="D23" s="9" t="inlineStr">
@@ -1925,17 +1925,17 @@
       </c>
       <c r="E23" s="4" t="inlineStr">
         <is>
-          <t>T-6 to T+2</t>
+          <t>T-2 to T+4</t>
         </is>
       </c>
       <c r="F23" s="4" t="inlineStr">
         <is>
-          <t>T - 6</t>
+          <t>T - 2</t>
         </is>
       </c>
       <c r="G23" s="4" t="inlineStr">
         <is>
-          <t>T + 2</t>
+          <t>T + 4</t>
         </is>
       </c>
       <c r="H23" s="4" t="inlineStr">
@@ -1945,17 +1945,17 @@
       </c>
       <c r="I23" s="4" t="inlineStr">
         <is>
-          <t>81.5%</t>
+          <t>81.7%</t>
         </is>
       </c>
       <c r="J23" s="7" t="inlineStr">
         <is>
-          <t>₹283,651</t>
+          <t>₹36,972</t>
         </is>
       </c>
       <c r="K23" s="7" t="inlineStr">
         <is>
-          <t>₹665,379</t>
+          <t>₹86,687</t>
         </is>
       </c>
       <c r="L23" s="10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="M23" s="5" t="inlineStr">
         <is>
-          <t>BUY FUTURES 6 trading days before T, Exit 2 days after T</t>
+          <t>BUY FUTURES 2 trading days before T, Exit 4 days after T</t>
         </is>
       </c>
       <c r="N23" s="5" t="inlineStr">
         <is>
-          <t>BUY CALL OPTION 6 trading days before T</t>
+          <t>BUY CALL OPTION 2 trading days before T</t>
         </is>
       </c>
     </row>
@@ -1980,27 +1980,27 @@
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>DRREDDY</t>
+          <t>HINDALCO</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>Dr Reddys Laboratories Ltd</t>
-        </is>
-      </c>
-      <c r="D24" s="6" t="inlineStr">
-        <is>
-          <t>SHORT</t>
+          <t>Hindalco Industries Ltd</t>
+        </is>
+      </c>
+      <c r="D24" s="9" t="inlineStr">
+        <is>
+          <t>LONG</t>
         </is>
       </c>
       <c r="E24" s="4" t="inlineStr">
         <is>
-          <t>T-3 to T+1</t>
+          <t>T-4 to T+1</t>
         </is>
       </c>
       <c r="F24" s="4" t="inlineStr">
         <is>
-          <t>T - 3</t>
+          <t>T - 4</t>
         </is>
       </c>
       <c r="G24" s="4" t="inlineStr">
@@ -2010,22 +2010,22 @@
       </c>
       <c r="H24" s="4" t="inlineStr">
         <is>
-          <t>83.0%</t>
+          <t>85.8%</t>
         </is>
       </c>
       <c r="I24" s="4" t="inlineStr">
         <is>
-          <t>81.4%</t>
+          <t>81.5%</t>
         </is>
       </c>
       <c r="J24" s="7" t="inlineStr">
         <is>
-          <t>₹27,259</t>
+          <t>₹287,445</t>
         </is>
       </c>
       <c r="K24" s="7" t="inlineStr">
         <is>
-          <t>₹65,699</t>
+          <t>₹670,270</t>
         </is>
       </c>
       <c r="L24" s="10" t="inlineStr">
@@ -2035,12 +2035,12 @@
       </c>
       <c r="M24" s="5" t="inlineStr">
         <is>
-          <t>SELL FUTURES 3 trading days before T, Exit 1 days after T</t>
+          <t>BUY FUTURES 4 trading days before T, Exit 1 days after T</t>
         </is>
       </c>
       <c r="N24" s="5" t="inlineStr">
         <is>
-          <t>BUY PUT OPTION 3 trading days before T</t>
+          <t>BUY CALL OPTION 4 trading days before T</t>
         </is>
       </c>
     </row>
@@ -2050,22 +2050,22 @@
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>SHRIRAMFIN</t>
+          <t>TATASTEEL</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>Shriram Finance Ltd</t>
-        </is>
-      </c>
-      <c r="D25" s="6" t="inlineStr">
-        <is>
-          <t>SHORT</t>
+          <t>Tata Steel Ltd</t>
+        </is>
+      </c>
+      <c r="D25" s="9" t="inlineStr">
+        <is>
+          <t>LONG</t>
         </is>
       </c>
       <c r="E25" s="4" t="inlineStr">
         <is>
-          <t>T-6 to T+3</t>
+          <t>T-6 to T+2</t>
         </is>
       </c>
       <c r="F25" s="4" t="inlineStr">
@@ -2075,27 +2075,27 @@
       </c>
       <c r="G25" s="4" t="inlineStr">
         <is>
-          <t>T + 3</t>
+          <t>T + 2</t>
         </is>
       </c>
       <c r="H25" s="4" t="inlineStr">
         <is>
-          <t>77.9%</t>
+          <t>85.3%</t>
         </is>
       </c>
       <c r="I25" s="4" t="inlineStr">
         <is>
-          <t>81.2%</t>
+          <t>81.5%</t>
         </is>
       </c>
       <c r="J25" s="7" t="inlineStr">
         <is>
-          <t>₹105,538</t>
+          <t>₹283,651</t>
         </is>
       </c>
       <c r="K25" s="7" t="inlineStr">
         <is>
-          <t>₹271,063</t>
+          <t>₹665,379</t>
         </is>
       </c>
       <c r="L25" s="10" t="inlineStr">
@@ -2105,12 +2105,12 @@
       </c>
       <c r="M25" s="5" t="inlineStr">
         <is>
-          <t>SELL FUTURES 6 trading days before T, Exit 3 days after T</t>
+          <t>BUY FUTURES 6 trading days before T, Exit 2 days after T</t>
         </is>
       </c>
       <c r="N25" s="5" t="inlineStr">
         <is>
-          <t>BUY PUT OPTION 6 trading days before T</t>
+          <t>BUY CALL OPTION 6 trading days before T</t>
         </is>
       </c>
     </row>
@@ -2120,52 +2120,52 @@
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>TRENT</t>
+          <t>DRREDDY</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>Trent Ltd</t>
-        </is>
-      </c>
-      <c r="D26" s="9" t="inlineStr">
-        <is>
-          <t>LONG</t>
+          <t>Dr Reddys Laboratories Ltd</t>
+        </is>
+      </c>
+      <c r="D26" s="6" t="inlineStr">
+        <is>
+          <t>SHORT</t>
         </is>
       </c>
       <c r="E26" s="4" t="inlineStr">
         <is>
-          <t>T-6 to T+3</t>
+          <t>T-3 to T+1</t>
         </is>
       </c>
       <c r="F26" s="4" t="inlineStr">
         <is>
-          <t>T - 6</t>
+          <t>T - 3</t>
         </is>
       </c>
       <c r="G26" s="4" t="inlineStr">
         <is>
-          <t>T + 3</t>
+          <t>T + 1</t>
         </is>
       </c>
       <c r="H26" s="4" t="inlineStr">
         <is>
-          <t>86.8%</t>
+          <t>83.0%</t>
         </is>
       </c>
       <c r="I26" s="4" t="inlineStr">
         <is>
-          <t>81.1%</t>
+          <t>81.4%</t>
         </is>
       </c>
       <c r="J26" s="7" t="inlineStr">
         <is>
-          <t>₹4,190</t>
+          <t>₹27,259</t>
         </is>
       </c>
       <c r="K26" s="7" t="inlineStr">
         <is>
-          <t>₹9,650</t>
+          <t>₹65,699</t>
         </is>
       </c>
       <c r="L26" s="10" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="M26" s="5" t="inlineStr">
         <is>
-          <t>BUY FUTURES 6 trading days before T, Exit 3 days after T</t>
+          <t>SELL FUTURES 3 trading days before T, Exit 1 days after T</t>
         </is>
       </c>
       <c r="N26" s="5" t="inlineStr">
         <is>
-          <t>BUY CALL OPTION 6 trading days before T</t>
+          <t>BUY PUT OPTION 3 trading days before T</t>
         </is>
       </c>
     </row>
@@ -2190,12 +2190,12 @@
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>ASIANPAINT</t>
+          <t>SHRIRAMFIN</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>Asian Paints Ltd</t>
+          <t>Shriram Finance Ltd</t>
         </is>
       </c>
       <c r="D27" s="6" t="inlineStr">
@@ -2205,37 +2205,37 @@
       </c>
       <c r="E27" s="4" t="inlineStr">
         <is>
-          <t>T-5 to T+4</t>
+          <t>T-6 to T+3</t>
         </is>
       </c>
       <c r="F27" s="4" t="inlineStr">
         <is>
-          <t>T - 5</t>
+          <t>T - 6</t>
         </is>
       </c>
       <c r="G27" s="4" t="inlineStr">
         <is>
-          <t>T + 4</t>
+          <t>T + 3</t>
         </is>
       </c>
       <c r="H27" s="4" t="inlineStr">
         <is>
-          <t>91.6%</t>
+          <t>77.9%</t>
         </is>
       </c>
       <c r="I27" s="4" t="inlineStr">
         <is>
-          <t>81.0%</t>
+          <t>81.2%</t>
         </is>
       </c>
       <c r="J27" s="7" t="inlineStr">
         <is>
-          <t>₹20,158</t>
+          <t>₹105,538</t>
         </is>
       </c>
       <c r="K27" s="7" t="inlineStr">
         <is>
-          <t>₹44,022</t>
+          <t>₹271,063</t>
         </is>
       </c>
       <c r="L27" s="10" t="inlineStr">
@@ -2245,12 +2245,12 @@
       </c>
       <c r="M27" s="5" t="inlineStr">
         <is>
-          <t>SELL FUTURES 5 trading days before T, Exit 4 days after T</t>
+          <t>SELL FUTURES 6 trading days before T, Exit 3 days after T</t>
         </is>
       </c>
       <c r="N27" s="5" t="inlineStr">
         <is>
-          <t>BUY PUT OPTION 5 trading days before T</t>
+          <t>BUY PUT OPTION 6 trading days before T</t>
         </is>
       </c>
     </row>
@@ -2260,12 +2260,12 @@
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>HINDUNILVR</t>
+          <t>ASIANPAINT</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>Hindustan Unilever Ltd</t>
+          <t>Asian Paints Ltd</t>
         </is>
       </c>
       <c r="D28" s="6" t="inlineStr">
@@ -2275,37 +2275,37 @@
       </c>
       <c r="E28" s="4" t="inlineStr">
         <is>
-          <t>T-3 to T+2</t>
+          <t>T-5 to T+4</t>
         </is>
       </c>
       <c r="F28" s="4" t="inlineStr">
         <is>
-          <t>T - 3</t>
+          <t>T - 5</t>
         </is>
       </c>
       <c r="G28" s="4" t="inlineStr">
         <is>
-          <t>T + 2</t>
+          <t>T + 4</t>
         </is>
       </c>
       <c r="H28" s="4" t="inlineStr">
         <is>
-          <t>75.1%</t>
+          <t>91.6%</t>
         </is>
       </c>
       <c r="I28" s="4" t="inlineStr">
         <is>
-          <t>80.9%</t>
+          <t>81.0%</t>
         </is>
       </c>
       <c r="J28" s="7" t="inlineStr">
         <is>
-          <t>₹12,247</t>
+          <t>₹20,158</t>
         </is>
       </c>
       <c r="K28" s="7" t="inlineStr">
         <is>
-          <t>₹32,623</t>
+          <t>₹44,022</t>
         </is>
       </c>
       <c r="L28" s="10" t="inlineStr">
@@ -2315,12 +2315,12 @@
       </c>
       <c r="M28" s="5" t="inlineStr">
         <is>
-          <t>SELL FUTURES 3 trading days before T, Exit 2 days after T</t>
+          <t>SELL FUTURES 5 trading days before T, Exit 4 days after T</t>
         </is>
       </c>
       <c r="N28" s="5" t="inlineStr">
         <is>
-          <t>BUY PUT OPTION 3 trading days before T</t>
+          <t>BUY PUT OPTION 5 trading days before T</t>
         </is>
       </c>
     </row>
@@ -2330,12 +2330,12 @@
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>NESTLEIND</t>
+          <t>HINDUNILVR</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>Nestle India Ltd</t>
+          <t>Hindustan Unilever Ltd</t>
         </is>
       </c>
       <c r="D29" s="6" t="inlineStr">
@@ -2345,7 +2345,7 @@
       </c>
       <c r="E29" s="4" t="inlineStr">
         <is>
-          <t>T-3 to T+1</t>
+          <t>T-3 to T+2</t>
         </is>
       </c>
       <c r="F29" s="4" t="inlineStr">
@@ -2355,27 +2355,27 @@
       </c>
       <c r="G29" s="4" t="inlineStr">
         <is>
-          <t>T + 1</t>
+          <t>T + 2</t>
         </is>
       </c>
       <c r="H29" s="4" t="inlineStr">
         <is>
-          <t>92.2%</t>
+          <t>75.1%</t>
         </is>
       </c>
       <c r="I29" s="4" t="inlineStr">
         <is>
-          <t>80.7%</t>
+          <t>80.9%</t>
         </is>
       </c>
       <c r="J29" s="7" t="inlineStr">
         <is>
-          <t>₹68,111</t>
+          <t>₹12,247</t>
         </is>
       </c>
       <c r="K29" s="7" t="inlineStr">
         <is>
-          <t>₹147,731</t>
+          <t>₹32,623</t>
         </is>
       </c>
       <c r="L29" s="10" t="inlineStr">
@@ -2385,7 +2385,7 @@
       </c>
       <c r="M29" s="5" t="inlineStr">
         <is>
-          <t>SELL FUTURES 3 trading days before T, Exit 1 days after T</t>
+          <t>SELL FUTURES 3 trading days before T, Exit 2 days after T</t>
         </is>
       </c>
       <c r="N29" s="5" t="inlineStr">
@@ -2400,52 +2400,52 @@
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>COALINDIA</t>
+          <t>NESTLEIND</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>Coal India Ltd</t>
-        </is>
-      </c>
-      <c r="D30" s="9" t="inlineStr">
-        <is>
-          <t>LONG</t>
+          <t>Nestle India Ltd</t>
+        </is>
+      </c>
+      <c r="D30" s="6" t="inlineStr">
+        <is>
+          <t>SHORT</t>
         </is>
       </c>
       <c r="E30" s="4" t="inlineStr">
         <is>
-          <t>T-7 to T+5</t>
+          <t>T-3 to T+1</t>
         </is>
       </c>
       <c r="F30" s="4" t="inlineStr">
         <is>
-          <t>T - 7</t>
+          <t>T - 3</t>
         </is>
       </c>
       <c r="G30" s="4" t="inlineStr">
         <is>
-          <t>T + 5</t>
+          <t>T + 1</t>
         </is>
       </c>
       <c r="H30" s="4" t="inlineStr">
         <is>
-          <t>70.7%</t>
+          <t>92.2%</t>
         </is>
       </c>
       <c r="I30" s="4" t="inlineStr">
         <is>
-          <t>80.6%</t>
+          <t>80.7%</t>
         </is>
       </c>
       <c r="J30" s="7" t="inlineStr">
         <is>
-          <t>₹446,304</t>
+          <t>₹68,111</t>
         </is>
       </c>
       <c r="K30" s="7" t="inlineStr">
         <is>
-          <t>₹1,263,066</t>
+          <t>₹147,731</t>
         </is>
       </c>
       <c r="L30" s="10" t="inlineStr">
@@ -2455,12 +2455,12 @@
       </c>
       <c r="M30" s="5" t="inlineStr">
         <is>
-          <t>BUY FUTURES 7 trading days before T, Exit 5 days after T</t>
+          <t>SELL FUTURES 3 trading days before T, Exit 1 days after T</t>
         </is>
       </c>
       <c r="N30" s="5" t="inlineStr">
         <is>
-          <t>BUY CALL OPTION 7 trading days before T</t>
+          <t>BUY PUT OPTION 3 trading days before T</t>
         </is>
       </c>
     </row>
@@ -2470,12 +2470,12 @@
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>BRITANNIA</t>
+          <t>COALINDIA</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>Britannia Industries Ltd</t>
+          <t>Coal India Ltd</t>
         </is>
       </c>
       <c r="D31" s="9" t="inlineStr">
@@ -2485,7 +2485,7 @@
       </c>
       <c r="E31" s="4" t="inlineStr">
         <is>
-          <t>T-7 to T+2</t>
+          <t>T-7 to T+5</t>
         </is>
       </c>
       <c r="F31" s="4" t="inlineStr">
@@ -2495,27 +2495,27 @@
       </c>
       <c r="G31" s="4" t="inlineStr">
         <is>
-          <t>T + 2</t>
+          <t>T + 5</t>
         </is>
       </c>
       <c r="H31" s="4" t="inlineStr">
         <is>
-          <t>82.9%</t>
+          <t>70.7%</t>
         </is>
       </c>
       <c r="I31" s="4" t="inlineStr">
         <is>
-          <t>80.5%</t>
+          <t>80.6%</t>
         </is>
       </c>
       <c r="J31" s="7" t="inlineStr">
         <is>
-          <t>₹38,258</t>
+          <t>₹446,304</t>
         </is>
       </c>
       <c r="K31" s="7" t="inlineStr">
         <is>
-          <t>₹92,254</t>
+          <t>₹1,263,066</t>
         </is>
       </c>
       <c r="L31" s="10" t="inlineStr">
@@ -2525,7 +2525,7 @@
       </c>
       <c r="M31" s="5" t="inlineStr">
         <is>
-          <t>BUY FUTURES 7 trading days before T, Exit 2 days after T</t>
+          <t>BUY FUTURES 7 trading days before T, Exit 5 days after T</t>
         </is>
       </c>
       <c r="N31" s="5" t="inlineStr">
@@ -2540,37 +2540,37 @@
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>BPCL</t>
+          <t>ONGC</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>Bharat Petroleum Corp Ltd</t>
-        </is>
-      </c>
-      <c r="D32" s="9" t="inlineStr">
-        <is>
-          <t>LONG</t>
+          <t>Oil &amp; Natural Gas Corp Ltd</t>
+        </is>
+      </c>
+      <c r="D32" s="6" t="inlineStr">
+        <is>
+          <t>SHORT</t>
         </is>
       </c>
       <c r="E32" s="4" t="inlineStr">
         <is>
-          <t>T-6 to T+3</t>
+          <t>T-4 to T+5</t>
         </is>
       </c>
       <c r="F32" s="4" t="inlineStr">
         <is>
-          <t>T - 6</t>
+          <t>T - 4</t>
         </is>
       </c>
       <c r="G32" s="4" t="inlineStr">
         <is>
-          <t>T + 3</t>
+          <t>T + 5</t>
         </is>
       </c>
       <c r="H32" s="4" t="inlineStr">
         <is>
-          <t>82.1%</t>
+          <t>89.6%</t>
         </is>
       </c>
       <c r="I32" s="4" t="inlineStr">
@@ -2580,12 +2580,12 @@
       </c>
       <c r="J32" s="7" t="inlineStr">
         <is>
-          <t>₹485,394</t>
+          <t>₹292,773</t>
         </is>
       </c>
       <c r="K32" s="7" t="inlineStr">
         <is>
-          <t>₹1,183,021</t>
+          <t>₹653,584</t>
         </is>
       </c>
       <c r="L32" s="10" t="inlineStr">
@@ -2595,12 +2595,12 @@
       </c>
       <c r="M32" s="5" t="inlineStr">
         <is>
-          <t>BUY FUTURES 6 trading days before T, Exit 3 days after T</t>
+          <t>SELL FUTURES 4 trading days before T, Exit 5 days after T</t>
         </is>
       </c>
       <c r="N32" s="5" t="inlineStr">
         <is>
-          <t>BUY CALL OPTION 6 trading days before T</t>
+          <t>BUY PUT OPTION 4 trading days before T</t>
         </is>
       </c>
     </row>
@@ -2610,12 +2610,12 @@
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>JIOFIN</t>
+          <t>RELIANCE</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>Jio Financial Services Ltd</t>
+          <t>Reliance Industries Ltd</t>
         </is>
       </c>
       <c r="D33" s="6" t="inlineStr">
@@ -2625,22 +2625,22 @@
       </c>
       <c r="E33" s="4" t="inlineStr">
         <is>
-          <t>T-4 to T+2</t>
+          <t>T-3 to T+5</t>
         </is>
       </c>
       <c r="F33" s="4" t="inlineStr">
         <is>
-          <t>T - 4</t>
+          <t>T - 3</t>
         </is>
       </c>
       <c r="G33" s="4" t="inlineStr">
         <is>
-          <t>T + 2</t>
+          <t>T + 5</t>
         </is>
       </c>
       <c r="H33" s="4" t="inlineStr">
         <is>
-          <t>87.5%</t>
+          <t>68.0%</t>
         </is>
       </c>
       <c r="I33" s="4" t="inlineStr">
@@ -2650,12 +2650,12 @@
       </c>
       <c r="J33" s="7" t="inlineStr">
         <is>
-          <t>₹507,462</t>
+          <t>₹13,042</t>
         </is>
       </c>
       <c r="K33" s="7" t="inlineStr">
         <is>
-          <t>₹1,159,382</t>
+          <t>₹38,341</t>
         </is>
       </c>
       <c r="L33" s="10" t="inlineStr">
@@ -2665,12 +2665,12 @@
       </c>
       <c r="M33" s="5" t="inlineStr">
         <is>
-          <t>SELL FUTURES 4 trading days before T, Exit 2 days after T</t>
+          <t>SELL FUTURES 3 trading days before T, Exit 5 days after T</t>
         </is>
       </c>
       <c r="N33" s="5" t="inlineStr">
         <is>
-          <t>BUY PUT OPTION 4 trading days before T</t>
+          <t>BUY PUT OPTION 3 trading days before T</t>
         </is>
       </c>
     </row>
@@ -2680,37 +2680,37 @@
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>ONGC</t>
+          <t>TRENT</t>
         </is>
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>Oil &amp; Natural Gas Corp Ltd</t>
-        </is>
-      </c>
-      <c r="D34" s="6" t="inlineStr">
-        <is>
-          <t>SHORT</t>
+          <t>Trent Ltd</t>
+        </is>
+      </c>
+      <c r="D34" s="9" t="inlineStr">
+        <is>
+          <t>LONG</t>
         </is>
       </c>
       <c r="E34" s="4" t="inlineStr">
         <is>
-          <t>T-4 to T+5</t>
+          <t>T-7 to T+1</t>
         </is>
       </c>
       <c r="F34" s="4" t="inlineStr">
         <is>
-          <t>T - 4</t>
+          <t>T - 7</t>
         </is>
       </c>
       <c r="G34" s="4" t="inlineStr">
         <is>
-          <t>T + 5</t>
+          <t>T + 1</t>
         </is>
       </c>
       <c r="H34" s="4" t="inlineStr">
         <is>
-          <t>89.6%</t>
+          <t>78.3%</t>
         </is>
       </c>
       <c r="I34" s="4" t="inlineStr">
@@ -2720,27 +2720,27 @@
       </c>
       <c r="J34" s="7" t="inlineStr">
         <is>
-          <t>₹292,773</t>
+          <t>₹14,666</t>
         </is>
       </c>
       <c r="K34" s="7" t="inlineStr">
         <is>
-          <t>₹653,584</t>
-        </is>
-      </c>
-      <c r="L34" s="10" t="inlineStr">
+          <t>₹79,050</t>
+        </is>
+      </c>
+      <c r="L34" s="8" t="inlineStr">
         <is>
           <t>NOT ANNOUNCED YET</t>
         </is>
       </c>
       <c r="M34" s="5" t="inlineStr">
         <is>
-          <t>SELL FUTURES 4 trading days before T, Exit 5 days after T</t>
+          <t>BUY FUTURES 7 trading days before T, Exit 1 days after T</t>
         </is>
       </c>
       <c r="N34" s="5" t="inlineStr">
         <is>
-          <t>BUY PUT OPTION 4 trading days before T</t>
+          <t>BUY CALL OPTION 7 trading days before T</t>
         </is>
       </c>
     </row>
@@ -2750,12 +2750,12 @@
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>RELIANCE</t>
+          <t>LT</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>Reliance Industries Ltd</t>
+          <t>Larsen &amp; Toubro Ltd</t>
         </is>
       </c>
       <c r="D35" s="6" t="inlineStr">
@@ -2765,37 +2765,37 @@
       </c>
       <c r="E35" s="4" t="inlineStr">
         <is>
-          <t>T-3 to T+5</t>
+          <t>T-6 to T+3</t>
         </is>
       </c>
       <c r="F35" s="4" t="inlineStr">
         <is>
-          <t>T - 3</t>
+          <t>T - 6</t>
         </is>
       </c>
       <c r="G35" s="4" t="inlineStr">
         <is>
-          <t>T + 5</t>
+          <t>T + 3</t>
         </is>
       </c>
       <c r="H35" s="4" t="inlineStr">
         <is>
-          <t>68.0%</t>
+          <t>69.6%</t>
         </is>
       </c>
       <c r="I35" s="4" t="inlineStr">
         <is>
-          <t>80.4%</t>
+          <t>80.3%</t>
         </is>
       </c>
       <c r="J35" s="7" t="inlineStr">
         <is>
-          <t>₹13,042</t>
+          <t>₹13,542</t>
         </is>
       </c>
       <c r="K35" s="7" t="inlineStr">
         <is>
-          <t>₹38,341</t>
+          <t>₹38,897</t>
         </is>
       </c>
       <c r="L35" s="10" t="inlineStr">
@@ -2805,12 +2805,12 @@
       </c>
       <c r="M35" s="5" t="inlineStr">
         <is>
-          <t>SELL FUTURES 3 trading days before T, Exit 5 days after T</t>
+          <t>SELL FUTURES 6 trading days before T, Exit 3 days after T</t>
         </is>
       </c>
       <c r="N35" s="5" t="inlineStr">
         <is>
-          <t>BUY PUT OPTION 3 trading days before T</t>
+          <t>BUY PUT OPTION 6 trading days before T</t>
         </is>
       </c>
     </row>
@@ -2820,37 +2820,37 @@
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>LT</t>
+          <t>TECHM</t>
         </is>
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>Larsen &amp; Toubro Ltd</t>
-        </is>
-      </c>
-      <c r="D36" s="6" t="inlineStr">
-        <is>
-          <t>SHORT</t>
+          <t>Tech Mahindra Ltd</t>
+        </is>
+      </c>
+      <c r="D36" s="9" t="inlineStr">
+        <is>
+          <t>LONG</t>
         </is>
       </c>
       <c r="E36" s="4" t="inlineStr">
         <is>
-          <t>T-6 to T+3</t>
+          <t>T-5 to T+2</t>
         </is>
       </c>
       <c r="F36" s="4" t="inlineStr">
         <is>
-          <t>T - 6</t>
+          <t>T - 5</t>
         </is>
       </c>
       <c r="G36" s="4" t="inlineStr">
         <is>
-          <t>T + 3</t>
+          <t>T + 2</t>
         </is>
       </c>
       <c r="H36" s="4" t="inlineStr">
         <is>
-          <t>69.6%</t>
+          <t>78.5%</t>
         </is>
       </c>
       <c r="I36" s="4" t="inlineStr">
@@ -2860,12 +2860,12 @@
       </c>
       <c r="J36" s="7" t="inlineStr">
         <is>
-          <t>₹13,542</t>
+          <t>₹27,664</t>
         </is>
       </c>
       <c r="K36" s="7" t="inlineStr">
         <is>
-          <t>₹38,897</t>
+          <t>₹70,472</t>
         </is>
       </c>
       <c r="L36" s="10" t="inlineStr">
@@ -2875,12 +2875,12 @@
       </c>
       <c r="M36" s="5" t="inlineStr">
         <is>
-          <t>SELL FUTURES 6 trading days before T, Exit 3 days after T</t>
+          <t>BUY FUTURES 5 trading days before T, Exit 2 days after T</t>
         </is>
       </c>
       <c r="N36" s="5" t="inlineStr">
         <is>
-          <t>BUY PUT OPTION 6 trading days before T</t>
+          <t>BUY CALL OPTION 5 trading days before T</t>
         </is>
       </c>
     </row>
@@ -2890,27 +2890,27 @@
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>TECHM</t>
+          <t>BAJAJFINSV</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>Tech Mahindra Ltd</t>
-        </is>
-      </c>
-      <c r="D37" s="9" t="inlineStr">
-        <is>
-          <t>LONG</t>
+          <t>Bajaj Finserv Ltd</t>
+        </is>
+      </c>
+      <c r="D37" s="6" t="inlineStr">
+        <is>
+          <t>SHORT</t>
         </is>
       </c>
       <c r="E37" s="4" t="inlineStr">
         <is>
-          <t>T-5 to T+2</t>
+          <t>T-4 to T+2</t>
         </is>
       </c>
       <c r="F37" s="4" t="inlineStr">
         <is>
-          <t>T - 5</t>
+          <t>T - 4</t>
         </is>
       </c>
       <c r="G37" s="4" t="inlineStr">
@@ -2920,22 +2920,22 @@
       </c>
       <c r="H37" s="4" t="inlineStr">
         <is>
-          <t>78.5%</t>
+          <t>77.1%</t>
         </is>
       </c>
       <c r="I37" s="4" t="inlineStr">
         <is>
-          <t>80.3%</t>
+          <t>80.2%</t>
         </is>
       </c>
       <c r="J37" s="7" t="inlineStr">
         <is>
-          <t>₹27,664</t>
+          <t>₹132,142</t>
         </is>
       </c>
       <c r="K37" s="7" t="inlineStr">
         <is>
-          <t>₹70,472</t>
+          <t>₹342,782</t>
         </is>
       </c>
       <c r="L37" s="10" t="inlineStr">
@@ -2945,12 +2945,12 @@
       </c>
       <c r="M37" s="5" t="inlineStr">
         <is>
-          <t>BUY FUTURES 5 trading days before T, Exit 2 days after T</t>
+          <t>SELL FUTURES 4 trading days before T, Exit 2 days after T</t>
         </is>
       </c>
       <c r="N37" s="5" t="inlineStr">
         <is>
-          <t>BUY CALL OPTION 5 trading days before T</t>
+          <t>BUY PUT OPTION 4 trading days before T</t>
         </is>
       </c>
     </row>
@@ -2960,37 +2960,37 @@
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>BAJAJFINSV</t>
+          <t>MARUTI</t>
         </is>
       </c>
       <c r="C38" s="5" t="inlineStr">
         <is>
-          <t>Bajaj Finserv Ltd</t>
-        </is>
-      </c>
-      <c r="D38" s="6" t="inlineStr">
-        <is>
-          <t>SHORT</t>
+          <t>Maruti Suzuki India Ltd</t>
+        </is>
+      </c>
+      <c r="D38" s="9" t="inlineStr">
+        <is>
+          <t>LONG</t>
         </is>
       </c>
       <c r="E38" s="4" t="inlineStr">
         <is>
-          <t>T-4 to T+2</t>
+          <t>T-7 to T+5</t>
         </is>
       </c>
       <c r="F38" s="4" t="inlineStr">
         <is>
-          <t>T - 4</t>
+          <t>T - 7</t>
         </is>
       </c>
       <c r="G38" s="4" t="inlineStr">
         <is>
-          <t>T + 2</t>
+          <t>T + 5</t>
         </is>
       </c>
       <c r="H38" s="4" t="inlineStr">
         <is>
-          <t>77.1%</t>
+          <t>80.8%</t>
         </is>
       </c>
       <c r="I38" s="4" t="inlineStr">
@@ -3000,12 +3000,12 @@
       </c>
       <c r="J38" s="7" t="inlineStr">
         <is>
-          <t>₹132,142</t>
+          <t>₹9,691</t>
         </is>
       </c>
       <c r="K38" s="7" t="inlineStr">
         <is>
-          <t>₹342,782</t>
+          <t>₹23,974</t>
         </is>
       </c>
       <c r="L38" s="10" t="inlineStr">
@@ -3015,12 +3015,12 @@
       </c>
       <c r="M38" s="5" t="inlineStr">
         <is>
-          <t>SELL FUTURES 4 trading days before T, Exit 2 days after T</t>
+          <t>BUY FUTURES 7 trading days before T, Exit 5 days after T</t>
         </is>
       </c>
       <c r="N38" s="5" t="inlineStr">
         <is>
-          <t>BUY PUT OPTION 4 trading days before T</t>
+          <t>BUY CALL OPTION 7 trading days before T</t>
         </is>
       </c>
     </row>
@@ -3030,52 +3030,52 @@
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>MARUTI</t>
+          <t>KOTAKBANK</t>
         </is>
       </c>
       <c r="C39" s="5" t="inlineStr">
         <is>
-          <t>Maruti Suzuki India Ltd</t>
-        </is>
-      </c>
-      <c r="D39" s="9" t="inlineStr">
-        <is>
-          <t>LONG</t>
+          <t>Kotak Mahindra Bank Ltd</t>
+        </is>
+      </c>
+      <c r="D39" s="6" t="inlineStr">
+        <is>
+          <t>SHORT</t>
         </is>
       </c>
       <c r="E39" s="4" t="inlineStr">
         <is>
-          <t>T-7 to T+5</t>
+          <t>T-2 to T+4</t>
         </is>
       </c>
       <c r="F39" s="4" t="inlineStr">
         <is>
-          <t>T - 7</t>
+          <t>T - 2</t>
         </is>
       </c>
       <c r="G39" s="4" t="inlineStr">
         <is>
-          <t>T + 5</t>
+          <t>T + 4</t>
         </is>
       </c>
       <c r="H39" s="4" t="inlineStr">
         <is>
-          <t>80.8%</t>
+          <t>77.5%</t>
         </is>
       </c>
       <c r="I39" s="4" t="inlineStr">
         <is>
-          <t>80.2%</t>
+          <t>80.0%</t>
         </is>
       </c>
       <c r="J39" s="7" t="inlineStr">
         <is>
-          <t>₹9,691</t>
+          <t>₹51,045</t>
         </is>
       </c>
       <c r="K39" s="7" t="inlineStr">
         <is>
-          <t>₹23,974</t>
+          <t>₹131,746</t>
         </is>
       </c>
       <c r="L39" s="10" t="inlineStr">
@@ -3085,12 +3085,12 @@
       </c>
       <c r="M39" s="5" t="inlineStr">
         <is>
-          <t>BUY FUTURES 7 trading days before T, Exit 5 days after T</t>
+          <t>SELL FUTURES 2 trading days before T, Exit 4 days after T</t>
         </is>
       </c>
       <c r="N39" s="5" t="inlineStr">
         <is>
-          <t>BUY CALL OPTION 7 trading days before T</t>
+          <t>BUY PUT OPTION 2 trading days before T</t>
         </is>
       </c>
     </row>
@@ -3100,12 +3100,12 @@
       </c>
       <c r="B40" s="5" t="inlineStr">
         <is>
-          <t>KOTAKBANK</t>
+          <t>TITAN</t>
         </is>
       </c>
       <c r="C40" s="5" t="inlineStr">
         <is>
-          <t>Kotak Mahindra Bank Ltd</t>
+          <t>Titan Company Ltd</t>
         </is>
       </c>
       <c r="D40" s="6" t="inlineStr">
@@ -3115,22 +3115,22 @@
       </c>
       <c r="E40" s="4" t="inlineStr">
         <is>
-          <t>T-2 to T+4</t>
+          <t>T-3 to T+3</t>
         </is>
       </c>
       <c r="F40" s="4" t="inlineStr">
         <is>
-          <t>T - 2</t>
+          <t>T - 3</t>
         </is>
       </c>
       <c r="G40" s="4" t="inlineStr">
         <is>
-          <t>T + 4</t>
+          <t>T + 3</t>
         </is>
       </c>
       <c r="H40" s="4" t="inlineStr">
         <is>
-          <t>77.5%</t>
+          <t>77.4%</t>
         </is>
       </c>
       <c r="I40" s="4" t="inlineStr">
@@ -3140,12 +3140,12 @@
       </c>
       <c r="J40" s="7" t="inlineStr">
         <is>
-          <t>₹51,045</t>
+          <t>₹19,919</t>
         </is>
       </c>
       <c r="K40" s="7" t="inlineStr">
         <is>
-          <t>₹131,746</t>
+          <t>₹51,444</t>
         </is>
       </c>
       <c r="L40" s="10" t="inlineStr">
@@ -3155,12 +3155,12 @@
       </c>
       <c r="M40" s="5" t="inlineStr">
         <is>
-          <t>SELL FUTURES 2 trading days before T, Exit 4 days after T</t>
+          <t>SELL FUTURES 3 trading days before T, Exit 3 days after T</t>
         </is>
       </c>
       <c r="N40" s="5" t="inlineStr">
         <is>
-          <t>BUY PUT OPTION 2 trading days before T</t>
+          <t>BUY PUT OPTION 3 trading days before T</t>
         </is>
       </c>
     </row>
@@ -3170,12 +3170,12 @@
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>TITAN</t>
+          <t>BAJAJ-AUTO</t>
         </is>
       </c>
       <c r="C41" s="5" t="inlineStr">
         <is>
-          <t>Titan Company Ltd</t>
+          <t>Bajaj Auto Ltd</t>
         </is>
       </c>
       <c r="D41" s="6" t="inlineStr">
@@ -3185,7 +3185,7 @@
       </c>
       <c r="E41" s="4" t="inlineStr">
         <is>
-          <t>T-3 to T+3</t>
+          <t>T-3 to T+2</t>
         </is>
       </c>
       <c r="F41" s="4" t="inlineStr">
@@ -3195,27 +3195,27 @@
       </c>
       <c r="G41" s="4" t="inlineStr">
         <is>
-          <t>T + 3</t>
+          <t>T + 2</t>
         </is>
       </c>
       <c r="H41" s="4" t="inlineStr">
         <is>
-          <t>77.4%</t>
+          <t>91.1%</t>
         </is>
       </c>
       <c r="I41" s="4" t="inlineStr">
         <is>
-          <t>80.0%</t>
+          <t>79.8%</t>
         </is>
       </c>
       <c r="J41" s="7" t="inlineStr">
         <is>
-          <t>₹19,919</t>
+          <t>₹6,642</t>
         </is>
       </c>
       <c r="K41" s="7" t="inlineStr">
         <is>
-          <t>₹51,444</t>
+          <t>₹14,581</t>
         </is>
       </c>
       <c r="L41" s="10" t="inlineStr">
@@ -3225,7 +3225,7 @@
       </c>
       <c r="M41" s="5" t="inlineStr">
         <is>
-          <t>SELL FUTURES 3 trading days before T, Exit 3 days after T</t>
+          <t>SELL FUTURES 3 trading days before T, Exit 2 days after T</t>
         </is>
       </c>
       <c r="N41" s="5" t="inlineStr">
@@ -3240,52 +3240,52 @@
       </c>
       <c r="B42" s="5" t="inlineStr">
         <is>
-          <t>TATAMOTORS</t>
+          <t>SUNPHARMA</t>
         </is>
       </c>
       <c r="C42" s="5" t="inlineStr">
         <is>
-          <t>Tata Motors Ltd</t>
-        </is>
-      </c>
-      <c r="D42" s="9" t="inlineStr">
-        <is>
-          <t>LONG</t>
+          <t>Sun Pharmaceutical Industries Ltd</t>
+        </is>
+      </c>
+      <c r="D42" s="6" t="inlineStr">
+        <is>
+          <t>SHORT</t>
         </is>
       </c>
       <c r="E42" s="4" t="inlineStr">
         <is>
-          <t>T-5 to T+5</t>
+          <t>T-3 to T+2</t>
         </is>
       </c>
       <c r="F42" s="4" t="inlineStr">
         <is>
-          <t>T - 5</t>
+          <t>T - 3</t>
         </is>
       </c>
       <c r="G42" s="4" t="inlineStr">
         <is>
-          <t>T + 5</t>
+          <t>T + 2</t>
         </is>
       </c>
       <c r="H42" s="4" t="inlineStr">
         <is>
-          <t>76.7%</t>
+          <t>91.9%</t>
         </is>
       </c>
       <c r="I42" s="4" t="inlineStr">
         <is>
-          <t>79.9%</t>
+          <t>79.6%</t>
         </is>
       </c>
       <c r="J42" s="7" t="inlineStr">
         <is>
-          <t>₹84,716</t>
+          <t>₹20,285</t>
         </is>
       </c>
       <c r="K42" s="7" t="inlineStr">
         <is>
-          <t>₹220,901</t>
+          <t>₹44,155</t>
         </is>
       </c>
       <c r="L42" s="10" t="inlineStr">
@@ -3295,12 +3295,12 @@
       </c>
       <c r="M42" s="5" t="inlineStr">
         <is>
-          <t>BUY FUTURES 5 trading days before T, Exit 5 days after T</t>
+          <t>SELL FUTURES 3 trading days before T, Exit 2 days after T</t>
         </is>
       </c>
       <c r="N42" s="5" t="inlineStr">
         <is>
-          <t>BUY CALL OPTION 5 trading days before T</t>
+          <t>BUY PUT OPTION 3 trading days before T</t>
         </is>
       </c>
     </row>
@@ -3310,12 +3310,12 @@
       </c>
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>BAJAJ-AUTO</t>
+          <t>SBIN</t>
         </is>
       </c>
       <c r="C43" s="5" t="inlineStr">
         <is>
-          <t>Bajaj Auto Ltd</t>
+          <t>State Bank of India</t>
         </is>
       </c>
       <c r="D43" s="6" t="inlineStr">
@@ -3325,37 +3325,37 @@
       </c>
       <c r="E43" s="4" t="inlineStr">
         <is>
-          <t>T-3 to T+2</t>
+          <t>T-4 to T+3</t>
         </is>
       </c>
       <c r="F43" s="4" t="inlineStr">
         <is>
-          <t>T - 3</t>
+          <t>T - 4</t>
         </is>
       </c>
       <c r="G43" s="4" t="inlineStr">
         <is>
-          <t>T + 2</t>
+          <t>T + 3</t>
         </is>
       </c>
       <c r="H43" s="4" t="inlineStr">
         <is>
-          <t>91.1%</t>
+          <t>83.3%</t>
         </is>
       </c>
       <c r="I43" s="4" t="inlineStr">
         <is>
-          <t>79.8%</t>
+          <t>79.5%</t>
         </is>
       </c>
       <c r="J43" s="7" t="inlineStr">
         <is>
-          <t>₹6,642</t>
+          <t>₹169,454</t>
         </is>
       </c>
       <c r="K43" s="7" t="inlineStr">
         <is>
-          <t>₹14,581</t>
+          <t>₹406,755</t>
         </is>
       </c>
       <c r="L43" s="10" t="inlineStr">
@@ -3365,12 +3365,12 @@
       </c>
       <c r="M43" s="5" t="inlineStr">
         <is>
-          <t>SELL FUTURES 3 trading days before T, Exit 2 days after T</t>
+          <t>SELL FUTURES 4 trading days before T, Exit 3 days after T</t>
         </is>
       </c>
       <c r="N43" s="5" t="inlineStr">
         <is>
-          <t>BUY PUT OPTION 3 trading days before T</t>
+          <t>BUY PUT OPTION 4 trading days before T</t>
         </is>
       </c>
     </row>
@@ -3380,12 +3380,12 @@
       </c>
       <c r="B44" s="5" t="inlineStr">
         <is>
-          <t>SUNPHARMA</t>
+          <t>M&amp;M</t>
         </is>
       </c>
       <c r="C44" s="5" t="inlineStr">
         <is>
-          <t>Sun Pharmaceutical Industries Ltd</t>
+          <t>Mahindra &amp; Mahindra Ltd</t>
         </is>
       </c>
       <c r="D44" s="6" t="inlineStr">
@@ -3395,37 +3395,37 @@
       </c>
       <c r="E44" s="4" t="inlineStr">
         <is>
-          <t>T-3 to T+2</t>
+          <t>T-2 to T+1</t>
         </is>
       </c>
       <c r="F44" s="4" t="inlineStr">
         <is>
-          <t>T - 3</t>
+          <t>T - 2</t>
         </is>
       </c>
       <c r="G44" s="4" t="inlineStr">
         <is>
-          <t>T + 2</t>
+          <t>T + 1</t>
         </is>
       </c>
       <c r="H44" s="4" t="inlineStr">
         <is>
-          <t>91.9%</t>
+          <t>72.3%</t>
         </is>
       </c>
       <c r="I44" s="4" t="inlineStr">
         <is>
-          <t>79.6%</t>
+          <t>79.4%</t>
         </is>
       </c>
       <c r="J44" s="7" t="inlineStr">
         <is>
-          <t>₹20,285</t>
+          <t>₹27,525</t>
         </is>
       </c>
       <c r="K44" s="7" t="inlineStr">
         <is>
-          <t>₹44,155</t>
+          <t>₹76,100</t>
         </is>
       </c>
       <c r="L44" s="10" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="M44" s="5" t="inlineStr">
         <is>
-          <t>SELL FUTURES 3 trading days before T, Exit 2 days after T</t>
+          <t>SELL FUTURES 2 trading days before T, Exit 1 days after T</t>
         </is>
       </c>
       <c r="N44" s="5" t="inlineStr">
         <is>
-          <t>BUY PUT OPTION 3 trading days before T</t>
+          <t>BUY PUT OPTION 2 trading days before T</t>
         </is>
       </c>
     </row>
@@ -3450,52 +3450,52 @@
       </c>
       <c r="B45" s="5" t="inlineStr">
         <is>
-          <t>SBIN</t>
+          <t>NTPC</t>
         </is>
       </c>
       <c r="C45" s="5" t="inlineStr">
         <is>
-          <t>State Bank of India</t>
-        </is>
-      </c>
-      <c r="D45" s="6" t="inlineStr">
-        <is>
-          <t>SHORT</t>
+          <t>NTPC Ltd</t>
+        </is>
+      </c>
+      <c r="D45" s="9" t="inlineStr">
+        <is>
+          <t>LONG</t>
         </is>
       </c>
       <c r="E45" s="4" t="inlineStr">
         <is>
-          <t>T-4 to T+3</t>
+          <t>T-3 to T+2</t>
         </is>
       </c>
       <c r="F45" s="4" t="inlineStr">
         <is>
-          <t>T - 4</t>
+          <t>T - 3</t>
         </is>
       </c>
       <c r="G45" s="4" t="inlineStr">
         <is>
-          <t>T + 3</t>
+          <t>T + 2</t>
         </is>
       </c>
       <c r="H45" s="4" t="inlineStr">
         <is>
-          <t>83.3%</t>
+          <t>82.5%</t>
         </is>
       </c>
       <c r="I45" s="4" t="inlineStr">
         <is>
-          <t>79.5%</t>
+          <t>79.4%</t>
         </is>
       </c>
       <c r="J45" s="7" t="inlineStr">
         <is>
-          <t>₹169,454</t>
+          <t>₹140,642</t>
         </is>
       </c>
       <c r="K45" s="7" t="inlineStr">
         <is>
-          <t>₹406,755</t>
+          <t>₹341,157</t>
         </is>
       </c>
       <c r="L45" s="10" t="inlineStr">
@@ -3505,12 +3505,12 @@
       </c>
       <c r="M45" s="5" t="inlineStr">
         <is>
-          <t>SELL FUTURES 4 trading days before T, Exit 3 days after T</t>
+          <t>BUY FUTURES 3 trading days before T, Exit 2 days after T</t>
         </is>
       </c>
       <c r="N45" s="5" t="inlineStr">
         <is>
-          <t>BUY PUT OPTION 4 trading days before T</t>
+          <t>BUY CALL OPTION 3 trading days before T</t>
         </is>
       </c>
     </row>
@@ -3520,52 +3520,52 @@
       </c>
       <c r="B46" s="5" t="inlineStr">
         <is>
-          <t>M&amp;M</t>
+          <t>BEL</t>
         </is>
       </c>
       <c r="C46" s="5" t="inlineStr">
         <is>
-          <t>Mahindra &amp; Mahindra Ltd</t>
-        </is>
-      </c>
-      <c r="D46" s="6" t="inlineStr">
-        <is>
-          <t>SHORT</t>
+          <t>Bharat Electronics Ltd</t>
+        </is>
+      </c>
+      <c r="D46" s="9" t="inlineStr">
+        <is>
+          <t>LONG</t>
         </is>
       </c>
       <c r="E46" s="4" t="inlineStr">
         <is>
-          <t>T-2 to T+1</t>
+          <t>T-6 to T+2</t>
         </is>
       </c>
       <c r="F46" s="4" t="inlineStr">
         <is>
-          <t>T - 2</t>
+          <t>T - 6</t>
         </is>
       </c>
       <c r="G46" s="4" t="inlineStr">
         <is>
-          <t>T + 1</t>
+          <t>T + 2</t>
         </is>
       </c>
       <c r="H46" s="4" t="inlineStr">
         <is>
-          <t>72.3%</t>
+          <t>77.2%</t>
         </is>
       </c>
       <c r="I46" s="4" t="inlineStr">
         <is>
-          <t>79.4%</t>
+          <t>79.1%</t>
         </is>
       </c>
       <c r="J46" s="7" t="inlineStr">
         <is>
-          <t>₹27,525</t>
+          <t>₹454,767</t>
         </is>
       </c>
       <c r="K46" s="7" t="inlineStr">
         <is>
-          <t>₹76,100</t>
+          <t>₹1,178,458</t>
         </is>
       </c>
       <c r="L46" s="10" t="inlineStr">
@@ -3575,12 +3575,12 @@
       </c>
       <c r="M46" s="5" t="inlineStr">
         <is>
-          <t>SELL FUTURES 2 trading days before T, Exit 1 days after T</t>
+          <t>BUY FUTURES 6 trading days before T, Exit 2 days after T</t>
         </is>
       </c>
       <c r="N46" s="5" t="inlineStr">
         <is>
-          <t>BUY PUT OPTION 2 trading days before T</t>
+          <t>BUY CALL OPTION 6 trading days before T</t>
         </is>
       </c>
     </row>
@@ -3590,12 +3590,12 @@
       </c>
       <c r="B47" s="5" t="inlineStr">
         <is>
-          <t>NTPC</t>
+          <t>JSWSTEEL</t>
         </is>
       </c>
       <c r="C47" s="5" t="inlineStr">
         <is>
-          <t>NTPC Ltd</t>
+          <t>JSW Steel Ltd</t>
         </is>
       </c>
       <c r="D47" s="9" t="inlineStr">
@@ -3605,37 +3605,37 @@
       </c>
       <c r="E47" s="4" t="inlineStr">
         <is>
-          <t>T-3 to T+2</t>
+          <t>T-6 to T+4</t>
         </is>
       </c>
       <c r="F47" s="4" t="inlineStr">
         <is>
-          <t>T - 3</t>
+          <t>T - 6</t>
         </is>
       </c>
       <c r="G47" s="4" t="inlineStr">
         <is>
-          <t>T + 2</t>
+          <t>T + 4</t>
         </is>
       </c>
       <c r="H47" s="4" t="inlineStr">
         <is>
-          <t>82.5%</t>
+          <t>74.6%</t>
         </is>
       </c>
       <c r="I47" s="4" t="inlineStr">
         <is>
-          <t>79.4%</t>
+          <t>79.0%</t>
         </is>
       </c>
       <c r="J47" s="7" t="inlineStr">
         <is>
-          <t>₹140,642</t>
+          <t>₹37,915</t>
         </is>
       </c>
       <c r="K47" s="7" t="inlineStr">
         <is>
-          <t>₹341,157</t>
+          <t>₹101,648</t>
         </is>
       </c>
       <c r="L47" s="10" t="inlineStr">
@@ -3645,12 +3645,12 @@
       </c>
       <c r="M47" s="5" t="inlineStr">
         <is>
-          <t>BUY FUTURES 3 trading days before T, Exit 2 days after T</t>
+          <t>BUY FUTURES 6 trading days before T, Exit 4 days after T</t>
         </is>
       </c>
       <c r="N47" s="5" t="inlineStr">
         <is>
-          <t>BUY CALL OPTION 3 trading days before T</t>
+          <t>BUY CALL OPTION 6 trading days before T</t>
         </is>
       </c>
     </row>
@@ -3660,52 +3660,52 @@
       </c>
       <c r="B48" s="5" t="inlineStr">
         <is>
-          <t>BEL</t>
+          <t>GRASIM</t>
         </is>
       </c>
       <c r="C48" s="5" t="inlineStr">
         <is>
-          <t>Bharat Electronics Ltd</t>
-        </is>
-      </c>
-      <c r="D48" s="9" t="inlineStr">
-        <is>
-          <t>LONG</t>
+          <t>Grasim Industries Ltd</t>
+        </is>
+      </c>
+      <c r="D48" s="6" t="inlineStr">
+        <is>
+          <t>SHORT</t>
         </is>
       </c>
       <c r="E48" s="4" t="inlineStr">
         <is>
-          <t>T-6 to T+2</t>
+          <t>T-2 to T+4</t>
         </is>
       </c>
       <c r="F48" s="4" t="inlineStr">
         <is>
-          <t>T - 6</t>
+          <t>T - 2</t>
         </is>
       </c>
       <c r="G48" s="4" t="inlineStr">
         <is>
-          <t>T + 2</t>
+          <t>T + 4</t>
         </is>
       </c>
       <c r="H48" s="4" t="inlineStr">
         <is>
-          <t>77.2%</t>
+          <t>74.5%</t>
         </is>
       </c>
       <c r="I48" s="4" t="inlineStr">
         <is>
-          <t>79.1%</t>
+          <t>78.9%</t>
         </is>
       </c>
       <c r="J48" s="7" t="inlineStr">
         <is>
-          <t>₹454,767</t>
+          <t>₹56,260</t>
         </is>
       </c>
       <c r="K48" s="7" t="inlineStr">
         <is>
-          <t>₹1,178,458</t>
+          <t>₹151,115</t>
         </is>
       </c>
       <c r="L48" s="10" t="inlineStr">
@@ -3715,12 +3715,12 @@
       </c>
       <c r="M48" s="5" t="inlineStr">
         <is>
-          <t>BUY FUTURES 6 trading days before T, Exit 2 days after T</t>
+          <t>SELL FUTURES 2 trading days before T, Exit 4 days after T</t>
         </is>
       </c>
       <c r="N48" s="5" t="inlineStr">
         <is>
-          <t>BUY CALL OPTION 6 trading days before T</t>
+          <t>BUY PUT OPTION 2 trading days before T</t>
         </is>
       </c>
     </row>
@@ -3730,52 +3730,52 @@
       </c>
       <c r="B49" s="5" t="inlineStr">
         <is>
-          <t>JSWSTEEL</t>
+          <t>BHARTIARTL</t>
         </is>
       </c>
       <c r="C49" s="5" t="inlineStr">
         <is>
-          <t>JSW Steel Ltd</t>
-        </is>
-      </c>
-      <c r="D49" s="9" t="inlineStr">
-        <is>
-          <t>LONG</t>
+          <t>Bharti Airtel Ltd</t>
+        </is>
+      </c>
+      <c r="D49" s="6" t="inlineStr">
+        <is>
+          <t>SHORT</t>
         </is>
       </c>
       <c r="E49" s="4" t="inlineStr">
         <is>
-          <t>T-6 to T+4</t>
+          <t>T-5 to T+2</t>
         </is>
       </c>
       <c r="F49" s="4" t="inlineStr">
         <is>
-          <t>T - 6</t>
+          <t>T - 5</t>
         </is>
       </c>
       <c r="G49" s="4" t="inlineStr">
         <is>
-          <t>T + 4</t>
+          <t>T + 2</t>
         </is>
       </c>
       <c r="H49" s="4" t="inlineStr">
         <is>
-          <t>74.6%</t>
+          <t>73.9%</t>
         </is>
       </c>
       <c r="I49" s="4" t="inlineStr">
         <is>
-          <t>79.0%</t>
+          <t>78.6%</t>
         </is>
       </c>
       <c r="J49" s="7" t="inlineStr">
         <is>
-          <t>₹37,915</t>
+          <t>₹85,394</t>
         </is>
       </c>
       <c r="K49" s="7" t="inlineStr">
         <is>
-          <t>₹101,648</t>
+          <t>₹231,044</t>
         </is>
       </c>
       <c r="L49" s="10" t="inlineStr">
@@ -3785,12 +3785,12 @@
       </c>
       <c r="M49" s="5" t="inlineStr">
         <is>
-          <t>BUY FUTURES 6 trading days before T, Exit 4 days after T</t>
+          <t>SELL FUTURES 5 trading days before T, Exit 2 days after T</t>
         </is>
       </c>
       <c r="N49" s="5" t="inlineStr">
         <is>
-          <t>BUY CALL OPTION 6 trading days before T</t>
+          <t>BUY PUT OPTION 5 trading days before T</t>
         </is>
       </c>
     </row>
@@ -3800,12 +3800,12 @@
       </c>
       <c r="B50" s="5" t="inlineStr">
         <is>
-          <t>GRASIM</t>
+          <t>POWERGRID</t>
         </is>
       </c>
       <c r="C50" s="5" t="inlineStr">
         <is>
-          <t>Grasim Industries Ltd</t>
+          <t>Power Grid Corporation of India Ltd</t>
         </is>
       </c>
       <c r="D50" s="6" t="inlineStr">
@@ -3815,37 +3815,37 @@
       </c>
       <c r="E50" s="4" t="inlineStr">
         <is>
-          <t>T-2 to T+4</t>
+          <t>T-3 to T+2</t>
         </is>
       </c>
       <c r="F50" s="4" t="inlineStr">
         <is>
-          <t>T - 2</t>
+          <t>T - 3</t>
         </is>
       </c>
       <c r="G50" s="4" t="inlineStr">
         <is>
-          <t>T + 4</t>
+          <t>T + 2</t>
         </is>
       </c>
       <c r="H50" s="4" t="inlineStr">
         <is>
-          <t>74.5%</t>
+          <t>71.8%</t>
         </is>
       </c>
       <c r="I50" s="4" t="inlineStr">
         <is>
-          <t>78.9%</t>
+          <t>77.7%</t>
         </is>
       </c>
       <c r="J50" s="7" t="inlineStr">
         <is>
-          <t>₹56,260</t>
+          <t>₹296,486</t>
         </is>
       </c>
       <c r="K50" s="7" t="inlineStr">
         <is>
-          <t>₹151,115</t>
+          <t>₹825,637</t>
         </is>
       </c>
       <c r="L50" s="10" t="inlineStr">
@@ -3855,12 +3855,12 @@
       </c>
       <c r="M50" s="5" t="inlineStr">
         <is>
-          <t>SELL FUTURES 2 trading days before T, Exit 4 days after T</t>
+          <t>SELL FUTURES 3 trading days before T, Exit 2 days after T</t>
         </is>
       </c>
       <c r="N50" s="5" t="inlineStr">
         <is>
-          <t>BUY PUT OPTION 2 trading days before T</t>
+          <t>BUY PUT OPTION 3 trading days before T</t>
         </is>
       </c>
     </row>
@@ -3870,67 +3870,67 @@
       </c>
       <c r="B51" s="5" t="inlineStr">
         <is>
-          <t>BHARTIARTL</t>
+          <t>INDIGO</t>
         </is>
       </c>
       <c r="C51" s="5" t="inlineStr">
         <is>
-          <t>Bharti Airtel Ltd</t>
-        </is>
-      </c>
-      <c r="D51" s="6" t="inlineStr">
-        <is>
-          <t>SHORT</t>
+          <t>InterGlobe Aviation Ltd</t>
+        </is>
+      </c>
+      <c r="D51" s="9" t="inlineStr">
+        <is>
+          <t>LONG</t>
         </is>
       </c>
       <c r="E51" s="4" t="inlineStr">
         <is>
-          <t>T-5 to T+2</t>
+          <t>T-8 to T+8</t>
         </is>
       </c>
       <c r="F51" s="4" t="inlineStr">
         <is>
-          <t>T - 5</t>
+          <t>T - 8</t>
         </is>
       </c>
       <c r="G51" s="4" t="inlineStr">
         <is>
-          <t>T + 2</t>
+          <t>T + 8</t>
         </is>
       </c>
       <c r="H51" s="4" t="inlineStr">
         <is>
-          <t>73.9%</t>
+          <t>69.6%</t>
         </is>
       </c>
       <c r="I51" s="4" t="inlineStr">
         <is>
-          <t>78.6%</t>
+          <t>77.6%</t>
         </is>
       </c>
       <c r="J51" s="7" t="inlineStr">
         <is>
-          <t>₹85,394</t>
+          <t>₹13,734</t>
         </is>
       </c>
       <c r="K51" s="7" t="inlineStr">
         <is>
-          <t>₹231,044</t>
-        </is>
-      </c>
-      <c r="L51" s="10" t="inlineStr">
+          <t>₹146,160</t>
+        </is>
+      </c>
+      <c r="L51" s="8" t="inlineStr">
         <is>
           <t>NOT ANNOUNCED YET</t>
         </is>
       </c>
       <c r="M51" s="5" t="inlineStr">
         <is>
-          <t>SELL FUTURES 5 trading days before T, Exit 2 days after T</t>
+          <t>BUY FUTURES 8 trading days before T, Exit 8 days after T</t>
         </is>
       </c>
       <c r="N51" s="5" t="inlineStr">
         <is>
-          <t>BUY PUT OPTION 5 trading days before T</t>
+          <t>BUY CALL OPTION 8 trading days before T</t>
         </is>
       </c>
     </row>
@@ -3940,12 +3940,12 @@
       </c>
       <c r="B52" s="5" t="inlineStr">
         <is>
-          <t>POWERGRID</t>
+          <t>TATACONSUM</t>
         </is>
       </c>
       <c r="C52" s="5" t="inlineStr">
         <is>
-          <t>Power Grid Corporation of India Ltd</t>
+          <t>Tata Consumer Products Ltd</t>
         </is>
       </c>
       <c r="D52" s="6" t="inlineStr">
@@ -3955,37 +3955,37 @@
       </c>
       <c r="E52" s="4" t="inlineStr">
         <is>
-          <t>T-3 to T+2</t>
+          <t>T-7 to T+5</t>
         </is>
       </c>
       <c r="F52" s="4" t="inlineStr">
         <is>
-          <t>T - 3</t>
+          <t>T - 7</t>
         </is>
       </c>
       <c r="G52" s="4" t="inlineStr">
         <is>
-          <t>T + 2</t>
+          <t>T + 5</t>
         </is>
       </c>
       <c r="H52" s="4" t="inlineStr">
         <is>
-          <t>71.8%</t>
+          <t>73.6%</t>
         </is>
       </c>
       <c r="I52" s="4" t="inlineStr">
         <is>
-          <t>77.7%</t>
+          <t>77.3%</t>
         </is>
       </c>
       <c r="J52" s="7" t="inlineStr">
         <is>
-          <t>₹296,486</t>
+          <t>₹115,130</t>
         </is>
       </c>
       <c r="K52" s="7" t="inlineStr">
         <is>
-          <t>₹825,637</t>
+          <t>₹312,982</t>
         </is>
       </c>
       <c r="L52" s="10" t="inlineStr">
@@ -3995,12 +3995,12 @@
       </c>
       <c r="M52" s="5" t="inlineStr">
         <is>
-          <t>SELL FUTURES 3 trading days before T, Exit 2 days after T</t>
+          <t>SELL FUTURES 7 trading days before T, Exit 5 days after T</t>
         </is>
       </c>
       <c r="N52" s="5" t="inlineStr">
         <is>
-          <t>BUY PUT OPTION 3 trading days before T</t>
+          <t>BUY PUT OPTION 7 trading days before T</t>
         </is>
       </c>
     </row>
@@ -4010,12 +4010,12 @@
       </c>
       <c r="B53" s="5" t="inlineStr">
         <is>
-          <t>TATACONSUM</t>
+          <t>BAJFINANCE</t>
         </is>
       </c>
       <c r="C53" s="5" t="inlineStr">
         <is>
-          <t>Tata Consumer Products Ltd</t>
+          <t>Bajaj Finance Ltd</t>
         </is>
       </c>
       <c r="D53" s="6" t="inlineStr">
@@ -4025,37 +4025,37 @@
       </c>
       <c r="E53" s="4" t="inlineStr">
         <is>
-          <t>T-7 to T+5</t>
+          <t>T-6 to T+4</t>
         </is>
       </c>
       <c r="F53" s="4" t="inlineStr">
         <is>
-          <t>T - 7</t>
+          <t>T - 6</t>
         </is>
       </c>
       <c r="G53" s="4" t="inlineStr">
         <is>
-          <t>T + 5</t>
+          <t>T + 4</t>
         </is>
       </c>
       <c r="H53" s="4" t="inlineStr">
         <is>
-          <t>73.6%</t>
+          <t>68.1%</t>
         </is>
       </c>
       <c r="I53" s="4" t="inlineStr">
         <is>
-          <t>77.3%</t>
+          <t>76.7%</t>
         </is>
       </c>
       <c r="J53" s="7" t="inlineStr">
         <is>
-          <t>₹115,130</t>
+          <t>₹4,234</t>
         </is>
       </c>
       <c r="K53" s="7" t="inlineStr">
         <is>
-          <t>₹312,982</t>
+          <t>₹12,436</t>
         </is>
       </c>
       <c r="L53" s="10" t="inlineStr">
@@ -4065,85 +4065,16 @@
       </c>
       <c r="M53" s="5" t="inlineStr">
         <is>
-          <t>SELL FUTURES 7 trading days before T, Exit 5 days after T</t>
+          <t>SELL FUTURES 6 trading days before T, Exit 4 days after T</t>
         </is>
       </c>
       <c r="N53" s="5" t="inlineStr">
         <is>
-          <t>BUY PUT OPTION 7 trading days before T</t>
-        </is>
-      </c>
-    </row>
-    <row r="54" ht="22" customHeight="1">
-      <c r="A54" s="4" t="n">
-        <v>50</v>
-      </c>
-      <c r="B54" s="5" t="inlineStr">
-        <is>
-          <t>BAJFINANCE</t>
-        </is>
-      </c>
-      <c r="C54" s="5" t="inlineStr">
-        <is>
-          <t>Bajaj Finance Ltd</t>
-        </is>
-      </c>
-      <c r="D54" s="6" t="inlineStr">
-        <is>
-          <t>SHORT</t>
-        </is>
-      </c>
-      <c r="E54" s="4" t="inlineStr">
-        <is>
-          <t>T-6 to T+4</t>
-        </is>
-      </c>
-      <c r="F54" s="4" t="inlineStr">
-        <is>
-          <t>T - 6</t>
-        </is>
-      </c>
-      <c r="G54" s="4" t="inlineStr">
-        <is>
-          <t>T + 4</t>
-        </is>
-      </c>
-      <c r="H54" s="4" t="inlineStr">
-        <is>
-          <t>68.1%</t>
-        </is>
-      </c>
-      <c r="I54" s="4" t="inlineStr">
-        <is>
-          <t>76.7%</t>
-        </is>
-      </c>
-      <c r="J54" s="7" t="inlineStr">
-        <is>
-          <t>₹4,234</t>
-        </is>
-      </c>
-      <c r="K54" s="7" t="inlineStr">
-        <is>
-          <t>₹12,436</t>
-        </is>
-      </c>
-      <c r="L54" s="10" t="inlineStr">
-        <is>
-          <t>NOT ANNOUNCED YET</t>
-        </is>
-      </c>
-      <c r="M54" s="5" t="inlineStr">
-        <is>
-          <t>SELL FUTURES 6 trading days before T, Exit 4 days after T</t>
-        </is>
-      </c>
-      <c r="N54" s="5" t="inlineStr">
-        <is>
           <t>BUY PUT OPTION 6 trading days before T</t>
         </is>
       </c>
     </row>
+    <row r="54" ht="22" customHeight="1"/>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A2:N2"/>
